--- a/US/US_Contenido_t.xlsx
+++ b/US/US_Contenido_t.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1449" uniqueCount="592">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1449" uniqueCount="593">
   <si>
     <t>.</t>
   </si>
@@ -1309,42 +1309,45 @@
     <t>1.75</t>
   </si>
   <si>
+    <t>320</t>
+  </si>
+  <si>
+    <t>400</t>
+  </si>
+  <si>
+    <t>820</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>540</t>
+  </si>
+  <si>
+    <t>440</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>360</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>135</t>
+  </si>
+  <si>
+    <t>432</t>
+  </si>
+  <si>
+    <t>240</t>
+  </si>
+  <si>
     <t>350</t>
   </si>
   <si>
-    <t>400</t>
-  </si>
-  <si>
-    <t>820</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>540</t>
-  </si>
-  <si>
-    <t>440</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>360</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>135</t>
-  </si>
-  <si>
-    <t>432</t>
-  </si>
-  <si>
-    <t>240</t>
-  </si>
-  <si>
     <t>500</t>
   </si>
   <si>
@@ -1450,9 +1453,6 @@
     <t>64</t>
   </si>
   <si>
-    <t>320</t>
-  </si>
-  <si>
     <t>25</t>
   </si>
   <si>
@@ -1514,6 +1514,9 @@
   </si>
   <si>
     <t>La Colonia # 1</t>
+  </si>
+  <si>
+    <t>1.9</t>
   </si>
   <si>
     <t>Pronto</t>
@@ -3910,47 +3913,47 @@
       <c r="Y2" s="1"/>
       <c r="Z2" s="1"/>
       <c r="AA2" s="1" t="s">
-        <v>431</v>
+        <v>443</v>
       </c>
       <c r="AB2" s="1" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AC2" s="1" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AD2" s="1" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AE2" s="1" t="s">
         <v>432</v>
       </c>
       <c r="AF2" s="1" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AG2" s="1" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AH2" s="1" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AI2" s="1"/>
       <c r="AJ2" s="1" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AK2" s="1" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AL2" s="1" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AM2" s="1" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AN2" s="1" t="s">
         <v>432</v>
       </c>
       <c r="AO2" s="1" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AP2" s="1" t="s">
         <v>439</v>
@@ -4002,26 +4005,26 @@
         <v>439</v>
       </c>
       <c r="BG2" s="1" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="BH2" s="1" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="BI2" s="1" t="s">
         <v>439</v>
       </c>
       <c r="BJ2" s="1"/>
       <c r="BK2" s="1" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="BL2" s="1" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="BM2" s="1" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="BN2" s="1" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="BO2" s="1" t="s">
         <v>439</v>
@@ -4034,80 +4037,80 @@
       <c r="BS2" s="1"/>
       <c r="BT2" s="1"/>
       <c r="BU2" s="1" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="BV2" s="1" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="BW2" s="1" t="s">
         <v>439</v>
       </c>
       <c r="BX2" s="1" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="BY2" s="1" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="BZ2" s="1" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="CA2" s="1" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="CB2" s="1"/>
       <c r="CC2" s="1" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="CD2" s="1" t="s">
         <v>432</v>
       </c>
       <c r="CE2" s="1" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="CF2" s="1"/>
       <c r="CG2" s="1" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="CH2" s="1" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="CI2" s="1"/>
       <c r="CJ2" s="1" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="CK2" s="1" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="CL2" s="1" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="CM2" s="1" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="CN2" s="1"/>
       <c r="CO2" s="1"/>
       <c r="CP2" s="1" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="CQ2" s="1" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="CR2" s="1"/>
       <c r="CS2" s="1" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="CT2" s="1"/>
       <c r="CU2" s="1" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="CV2" s="1" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="CW2" s="1" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="CX2" s="1" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="CY2" s="1" t="s">
         <v>432</v>
@@ -4152,7 +4155,7 @@
         <v>439</v>
       </c>
       <c r="DO2" s="1" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="DP2" s="1" t="s">
         <v>439</v>
@@ -4183,7 +4186,7 @@
         <v>439</v>
       </c>
       <c r="EB2" s="1" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="EC2" s="1" t="s">
         <v>439</v>
@@ -4205,50 +4208,50 @@
       </c>
       <c r="EI2" s="1"/>
       <c r="EJ2" s="1" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="EK2" s="1" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="EL2" s="1"/>
       <c r="EM2" s="1"/>
       <c r="EN2" s="1" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="EO2" s="1" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="EP2" s="1" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="EQ2" s="1" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="ER2" s="1"/>
       <c r="ES2" s="1" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="ET2" s="1" t="s">
         <v>439</v>
       </c>
       <c r="EU2" s="1"/>
       <c r="EV2" s="1" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="EW2" s="1" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="EX2" s="1" t="s">
         <v>439</v>
       </c>
       <c r="EY2" s="1" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="EZ2" s="1" t="s">
-        <v>478</v>
+        <v>431</v>
       </c>
       <c r="FA2" s="1" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="FB2" s="1" t="s">
         <v>432</v>
@@ -4260,7 +4263,7 @@
         <v>479</v>
       </c>
       <c r="FE2" s="1" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="FF2" s="1" t="s">
         <v>480</v>
@@ -4275,7 +4278,7 @@
         <v>482</v>
       </c>
       <c r="FJ2" s="1" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="FK2" s="1" t="s">
         <v>439</v>
@@ -4290,7 +4293,7 @@
         <v>485</v>
       </c>
       <c r="FO2" s="1" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="FP2" s="1" t="s">
         <v>486</v>
@@ -4303,13 +4306,13 @@
         <v>432</v>
       </c>
       <c r="FT2" s="1" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="FU2" s="1" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="FV2" s="1" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="FW2" s="1" t="s">
         <v>488</v>
@@ -4321,22 +4324,22 @@
         <v>490</v>
       </c>
       <c r="FZ2" s="1" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="GA2" s="1" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="GB2" s="1" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="GC2" s="1" t="s">
         <v>491</v>
       </c>
       <c r="GD2" s="1" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="GE2" s="1" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="GF2" s="1" t="s">
         <v>492</v>
@@ -4345,7 +4348,7 @@
         <v>493</v>
       </c>
       <c r="GH2" s="1" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="GI2" s="1" t="s">
         <v>492</v>
@@ -4540,13 +4543,13 @@
         <v>496</v>
       </c>
       <c r="ME2" s="1" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="MF2" s="1" t="s">
         <v>497</v>
       </c>
       <c r="MG2" s="1" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="MH2" s="1" t="s">
         <v>439</v>
@@ -4662,11 +4665,11 @@
         <v>429</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>430</v>
+        <v>500</v>
       </c>
       <c r="E3" s="1"/>
       <c r="F3" s="1" t="s">
-        <v>431</v>
+        <v>443</v>
       </c>
       <c r="G3" s="1"/>
       <c r="H3" s="1" t="s">
@@ -4713,47 +4716,47 @@
       <c r="Y3" s="1"/>
       <c r="Z3" s="1"/>
       <c r="AA3" s="1" t="s">
-        <v>431</v>
+        <v>443</v>
       </c>
       <c r="AB3" s="1" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AC3" s="1" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AD3" s="1" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AE3" s="1" t="s">
         <v>432</v>
       </c>
       <c r="AF3" s="1" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AG3" s="1" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AH3" s="1" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AI3" s="1"/>
       <c r="AJ3" s="1" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AK3" s="1" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AL3" s="1" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AM3" s="1" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AN3" s="1" t="s">
         <v>432</v>
       </c>
       <c r="AO3" s="1" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AP3" s="1" t="s">
         <v>439</v>
@@ -4805,26 +4808,26 @@
         <v>439</v>
       </c>
       <c r="BG3" s="1" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="BH3" s="1" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="BI3" s="1" t="s">
         <v>439</v>
       </c>
       <c r="BJ3" s="1"/>
       <c r="BK3" s="1" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="BL3" s="1" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="BM3" s="1" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="BN3" s="1" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="BO3" s="1" t="s">
         <v>439</v>
@@ -4837,80 +4840,80 @@
       <c r="BS3" s="1"/>
       <c r="BT3" s="1"/>
       <c r="BU3" s="1" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="BV3" s="1" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="BW3" s="1" t="s">
         <v>439</v>
       </c>
       <c r="BX3" s="1" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="BY3" s="1" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="BZ3" s="1" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="CA3" s="1" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="CB3" s="1"/>
       <c r="CC3" s="1" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="CD3" s="1" t="s">
         <v>432</v>
       </c>
       <c r="CE3" s="1" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="CF3" s="1"/>
       <c r="CG3" s="1" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="CH3" s="1" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="CI3" s="1"/>
       <c r="CJ3" s="1" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="CK3" s="1" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="CL3" s="1" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="CM3" s="1" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="CN3" s="1"/>
       <c r="CO3" s="1"/>
       <c r="CP3" s="1" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="CQ3" s="1" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="CR3" s="1"/>
       <c r="CS3" s="1" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="CT3" s="1"/>
       <c r="CU3" s="1" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="CV3" s="1" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="CW3" s="1" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="CX3" s="1" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="CY3" s="1" t="s">
         <v>432</v>
@@ -4955,7 +4958,7 @@
         <v>439</v>
       </c>
       <c r="DO3" s="1" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="DP3" s="1" t="s">
         <v>439</v>
@@ -4986,7 +4989,7 @@
         <v>439</v>
       </c>
       <c r="EB3" s="1" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="EC3" s="1" t="s">
         <v>439</v>
@@ -5008,50 +5011,50 @@
       </c>
       <c r="EI3" s="1"/>
       <c r="EJ3" s="1" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="EK3" s="1" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="EL3" s="1"/>
       <c r="EM3" s="1"/>
       <c r="EN3" s="1" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="EO3" s="1" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="EP3" s="1" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="EQ3" s="1" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="ER3" s="1"/>
       <c r="ES3" s="1" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="ET3" s="1" t="s">
         <v>439</v>
       </c>
       <c r="EU3" s="1"/>
       <c r="EV3" s="1" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="EW3" s="1" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="EX3" s="1" t="s">
         <v>439</v>
       </c>
       <c r="EY3" s="1" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="EZ3" s="1" t="s">
-        <v>478</v>
+        <v>431</v>
       </c>
       <c r="FA3" s="1" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="FB3" s="1" t="s">
         <v>432</v>
@@ -5063,7 +5066,7 @@
         <v>479</v>
       </c>
       <c r="FE3" s="1" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="FF3" s="1" t="s">
         <v>480</v>
@@ -5078,7 +5081,7 @@
         <v>482</v>
       </c>
       <c r="FJ3" s="1" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="FK3" s="1" t="s">
         <v>439</v>
@@ -5093,7 +5096,7 @@
         <v>485</v>
       </c>
       <c r="FO3" s="1" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="FP3" s="1" t="s">
         <v>486</v>
@@ -5106,13 +5109,13 @@
         <v>432</v>
       </c>
       <c r="FT3" s="1" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="FU3" s="1" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="FV3" s="1" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="FW3" s="1" t="s">
         <v>488</v>
@@ -5124,22 +5127,22 @@
         <v>490</v>
       </c>
       <c r="FZ3" s="1" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="GA3" s="1" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="GB3" s="1" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="GC3" s="1" t="s">
         <v>491</v>
       </c>
       <c r="GD3" s="1" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="GE3" s="1" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="GF3" s="1" t="s">
         <v>492</v>
@@ -5148,7 +5151,7 @@
         <v>493</v>
       </c>
       <c r="GH3" s="1" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="GI3" s="1" t="s">
         <v>492</v>
@@ -5343,13 +5346,13 @@
         <v>496</v>
       </c>
       <c r="ME3" s="1" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="MF3" s="1" t="s">
         <v>497</v>
       </c>
       <c r="MG3" s="1" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="MH3" s="1" t="s">
         <v>439</v>
@@ -5456,13 +5459,13 @@
     </row>
     <row r="4" spans="1:427">
       <c r="A4" s="1" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
@@ -5604,7 +5607,7 @@
       <c r="EK4" s="1"/>
       <c r="EL4" s="1"/>
       <c r="EM4" s="1" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="EN4" s="1"/>
       <c r="EO4" s="1"/>
@@ -5893,13 +5896,13 @@
     </row>
     <row r="5" spans="1:427">
       <c r="A5" s="1" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="D5" s="1"/>
       <c r="E5" s="1"/>
@@ -6041,7 +6044,7 @@
       <c r="EK5" s="1"/>
       <c r="EL5" s="1"/>
       <c r="EM5" s="1" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="EN5" s="1"/>
       <c r="EO5" s="1"/>
@@ -6330,13 +6333,13 @@
     </row>
     <row r="6" spans="1:427">
       <c r="A6" s="1" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="D6" s="1"/>
       <c r="E6" s="1" t="s">
@@ -6374,7 +6377,7 @@
       <c r="AG6" s="1"/>
       <c r="AH6" s="1"/>
       <c r="AI6" s="1" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="AJ6" s="1"/>
       <c r="AK6" s="1"/>
@@ -6423,7 +6426,7 @@
       <c r="BZ6" s="1"/>
       <c r="CA6" s="1"/>
       <c r="CB6" s="1" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="CC6" s="1"/>
       <c r="CD6" s="1"/>
@@ -6432,7 +6435,7 @@
       <c r="CG6" s="1"/>
       <c r="CH6" s="1"/>
       <c r="CI6" s="1" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="CJ6" s="1"/>
       <c r="CK6" s="1"/>
@@ -6445,11 +6448,11 @@
       <c r="CP6" s="1"/>
       <c r="CQ6" s="1"/>
       <c r="CR6" s="1" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="CS6" s="1"/>
       <c r="CT6" s="1" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="CU6" s="1"/>
       <c r="CV6" s="1"/>
@@ -6505,12 +6508,12 @@
       <c r="EP6" s="1"/>
       <c r="EQ6" s="1"/>
       <c r="ER6" s="1" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="ES6" s="1"/>
       <c r="ET6" s="1"/>
       <c r="EU6" s="1" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="EV6" s="1"/>
       <c r="EW6" s="1"/>
@@ -6534,7 +6537,7 @@
       <c r="FO6" s="1"/>
       <c r="FP6" s="1"/>
       <c r="FQ6" s="1" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="FR6" s="1"/>
       <c r="FS6" s="1"/>
@@ -6795,13 +6798,13 @@
     </row>
     <row r="7" spans="1:427">
       <c r="A7" s="1" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="D7" s="1"/>
       <c r="E7" s="1" t="s">
@@ -6839,7 +6842,7 @@
       <c r="AG7" s="1"/>
       <c r="AH7" s="1"/>
       <c r="AI7" s="1" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="AJ7" s="1"/>
       <c r="AK7" s="1"/>
@@ -6888,7 +6891,7 @@
       <c r="BZ7" s="1"/>
       <c r="CA7" s="1"/>
       <c r="CB7" s="1" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="CC7" s="1"/>
       <c r="CD7" s="1"/>
@@ -6897,7 +6900,7 @@
       <c r="CG7" s="1"/>
       <c r="CH7" s="1"/>
       <c r="CI7" s="1" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="CJ7" s="1"/>
       <c r="CK7" s="1"/>
@@ -6910,11 +6913,11 @@
       <c r="CP7" s="1"/>
       <c r="CQ7" s="1"/>
       <c r="CR7" s="1" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="CS7" s="1"/>
       <c r="CT7" s="1" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="CU7" s="1"/>
       <c r="CV7" s="1"/>
@@ -6970,12 +6973,12 @@
       <c r="EP7" s="1"/>
       <c r="EQ7" s="1"/>
       <c r="ER7" s="1" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="ES7" s="1"/>
       <c r="ET7" s="1"/>
       <c r="EU7" s="1" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="EV7" s="1"/>
       <c r="EW7" s="1"/>
@@ -6999,7 +7002,7 @@
       <c r="FO7" s="1"/>
       <c r="FP7" s="1"/>
       <c r="FQ7" s="1" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="FR7" s="1"/>
       <c r="FS7" s="1"/>
@@ -7260,13 +7263,13 @@
     </row>
     <row r="8" spans="1:427">
       <c r="A8" s="1" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
@@ -7697,13 +7700,13 @@
     </row>
     <row r="9" spans="1:427">
       <c r="A9" s="1" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="D9" s="1"/>
       <c r="E9" s="1"/>
@@ -8134,13 +8137,13 @@
     </row>
     <row r="10" spans="1:427">
       <c r="A10" s="1" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
@@ -8605,13 +8608,13 @@
     </row>
     <row r="11" spans="1:427">
       <c r="A11" s="1" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
@@ -9076,13 +9079,13 @@
     </row>
     <row r="12" spans="1:427">
       <c r="A12" s="1" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="D12" s="1"/>
       <c r="E12" s="1"/>
@@ -9513,13 +9516,13 @@
     </row>
     <row r="13" spans="1:427">
       <c r="A13" s="1" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
@@ -9950,13 +9953,13 @@
     </row>
     <row r="14" spans="1:427">
       <c r="A14" s="1" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
@@ -10401,13 +10404,13 @@
     </row>
     <row r="15" spans="1:427">
       <c r="A15" s="1" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="D15" s="1"/>
       <c r="E15" s="1"/>
@@ -10852,13 +10855,13 @@
     </row>
     <row r="16" spans="1:427">
       <c r="A16" s="1" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="D16" s="1"/>
       <c r="E16" s="1"/>
@@ -11295,13 +11298,13 @@
     </row>
     <row r="17" spans="1:427">
       <c r="A17" s="1" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="D17" s="1"/>
       <c r="E17" s="1"/>
@@ -11738,13 +11741,13 @@
     </row>
     <row r="18" spans="1:427">
       <c r="A18" s="1" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="D18" s="1"/>
       <c r="E18" s="1"/>
@@ -12179,13 +12182,13 @@
     </row>
     <row r="19" spans="1:427">
       <c r="A19" s="1" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="D19" s="1"/>
       <c r="E19" s="1"/>
@@ -12620,13 +12623,13 @@
     </row>
     <row r="20" spans="1:427">
       <c r="A20" s="1" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="D20" s="1"/>
       <c r="E20" s="1"/>
@@ -13071,13 +13074,13 @@
     </row>
     <row r="21" spans="1:427">
       <c r="A21" s="1" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="D21" s="1"/>
       <c r="E21" s="1"/>
@@ -13522,13 +13525,13 @@
     </row>
     <row r="22" spans="1:427">
       <c r="A22" s="1" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="D22" s="1"/>
       <c r="E22" s="1"/>
@@ -13865,7 +13868,7 @@
       <c r="LX22" s="1"/>
       <c r="LY22" s="1"/>
       <c r="LZ22" s="1" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="MA22" s="1"/>
       <c r="MB22" s="1"/>
@@ -13959,13 +13962,13 @@
     </row>
     <row r="23" spans="1:427">
       <c r="A23" s="1" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="D23" s="1"/>
       <c r="E23" s="1"/>
@@ -14302,7 +14305,7 @@
       <c r="LX23" s="1"/>
       <c r="LY23" s="1"/>
       <c r="LZ23" s="1" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="MA23" s="1"/>
       <c r="MB23" s="1"/>
@@ -14396,13 +14399,13 @@
     </row>
     <row r="24" spans="1:427">
       <c r="A24" s="1" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="D24" s="1"/>
       <c r="E24" s="1"/>
@@ -14763,7 +14766,7 @@
         <v>439</v>
       </c>
       <c r="MT24" s="1" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="MU24" s="1" t="s">
         <v>439</v>
@@ -14775,13 +14778,13 @@
         <v>437</v>
       </c>
       <c r="MX24" s="1" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="MY24" s="1" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="MZ24" s="1" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="NA24" s="1" t="s">
         <v>439</v>
@@ -14796,22 +14799,22 @@
         <v>439</v>
       </c>
       <c r="NE24" s="1" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="NF24" s="1" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="NG24" s="1" t="s">
         <v>490</v>
       </c>
       <c r="NH24" s="1" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="NI24" s="1" t="s">
         <v>491</v>
       </c>
       <c r="NJ24" s="1" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="NK24" s="1" t="s">
         <v>480</v>
@@ -14832,7 +14835,7 @@
         <v>439</v>
       </c>
       <c r="NQ24" s="1" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="NR24" s="1" t="s">
         <v>439</v>
@@ -14844,22 +14847,22 @@
         <v>483</v>
       </c>
       <c r="NU24" s="1" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="NV24" s="1" t="s">
         <v>439</v>
       </c>
       <c r="NW24" s="1" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="NX24" s="1" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="NY24" s="1" t="s">
         <v>439</v>
       </c>
       <c r="NZ24" s="1" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="OA24" s="1" t="s">
         <v>439</v>
@@ -14868,13 +14871,13 @@
         <v>439</v>
       </c>
       <c r="OC24" s="1" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="OD24" s="1" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="OE24" s="1" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="OF24" s="1" t="s">
         <v>495</v>
@@ -14883,7 +14886,7 @@
         <v>439</v>
       </c>
       <c r="OH24" s="1" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="OI24" s="1" t="s">
         <v>442</v>
@@ -14901,10 +14904,10 @@
         <v>480</v>
       </c>
       <c r="ON24" s="1" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="OO24" s="1" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="OP24" s="1" t="s">
         <v>437</v>
@@ -14935,13 +14938,13 @@
     </row>
     <row r="25" spans="1:427">
       <c r="A25" s="1" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="D25" s="1"/>
       <c r="E25" s="1"/>
@@ -15302,7 +15305,7 @@
         <v>439</v>
       </c>
       <c r="MT25" s="1" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="MU25" s="1" t="s">
         <v>439</v>
@@ -15314,13 +15317,13 @@
         <v>437</v>
       </c>
       <c r="MX25" s="1" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="MY25" s="1" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="MZ25" s="1" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="NA25" s="1" t="s">
         <v>439</v>
@@ -15335,22 +15338,22 @@
         <v>439</v>
       </c>
       <c r="NE25" s="1" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="NF25" s="1" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="NG25" s="1" t="s">
         <v>490</v>
       </c>
       <c r="NH25" s="1" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="NI25" s="1" t="s">
         <v>491</v>
       </c>
       <c r="NJ25" s="1" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="NK25" s="1" t="s">
         <v>480</v>
@@ -15371,7 +15374,7 @@
         <v>439</v>
       </c>
       <c r="NQ25" s="1" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="NR25" s="1" t="s">
         <v>439</v>
@@ -15383,22 +15386,22 @@
         <v>483</v>
       </c>
       <c r="NU25" s="1" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="NV25" s="1" t="s">
         <v>439</v>
       </c>
       <c r="NW25" s="1" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="NX25" s="1" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="NY25" s="1" t="s">
         <v>439</v>
       </c>
       <c r="NZ25" s="1" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="OA25" s="1" t="s">
         <v>439</v>
@@ -15407,13 +15410,13 @@
         <v>439</v>
       </c>
       <c r="OC25" s="1" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="OD25" s="1" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="OE25" s="1" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="OF25" s="1" t="s">
         <v>495</v>
@@ -15422,7 +15425,7 @@
         <v>439</v>
       </c>
       <c r="OH25" s="1" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="OI25" s="1" t="s">
         <v>442</v>
@@ -15440,10 +15443,10 @@
         <v>480</v>
       </c>
       <c r="ON25" s="1" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="OO25" s="1" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="OP25" s="1" t="s">
         <v>437</v>
@@ -15474,13 +15477,13 @@
     </row>
     <row r="26" spans="1:427">
       <c r="A26" s="1" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="D26" s="1"/>
       <c r="E26" s="1"/>
@@ -15915,13 +15918,13 @@
     </row>
     <row r="27" spans="1:427">
       <c r="A27" s="1" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="D27" s="1"/>
       <c r="E27" s="1"/>
@@ -16356,13 +16359,13 @@
     </row>
     <row r="28" spans="1:427">
       <c r="A28" s="1" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="D28" s="1"/>
       <c r="E28" s="1"/>
@@ -16813,13 +16816,13 @@
     </row>
     <row r="29" spans="1:427">
       <c r="A29" s="1" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="D29" s="1"/>
       <c r="E29" s="1"/>
@@ -17270,13 +17273,13 @@
     </row>
     <row r="30" spans="1:427">
       <c r="A30" s="1" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="D30" s="1"/>
       <c r="E30" s="1"/>
@@ -17711,13 +17714,13 @@
     </row>
     <row r="31" spans="1:427">
       <c r="A31" s="1" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="D31" s="1"/>
       <c r="E31" s="1"/>
@@ -18152,13 +18155,13 @@
     </row>
     <row r="32" spans="1:427">
       <c r="A32" s="1" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="D32" s="1"/>
       <c r="E32" s="1"/>
@@ -18589,13 +18592,13 @@
     </row>
     <row r="33" spans="1:427">
       <c r="A33" s="1" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="D33" s="1"/>
       <c r="E33" s="1"/>
@@ -19026,13 +19029,13 @@
     </row>
     <row r="34" spans="1:427">
       <c r="A34" s="1" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="D34" s="1"/>
       <c r="E34" s="1"/>
@@ -19465,13 +19468,13 @@
     </row>
     <row r="35" spans="1:427">
       <c r="A35" s="1" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="D35" s="1"/>
       <c r="E35" s="1"/>
@@ -19904,13 +19907,13 @@
     </row>
     <row r="36" spans="1:427">
       <c r="A36" s="1" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="D36" s="1"/>
       <c r="E36" s="1"/>
@@ -20343,13 +20346,13 @@
     </row>
     <row r="37" spans="1:427">
       <c r="A37" s="1" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="D37" s="1"/>
       <c r="E37" s="1"/>
@@ -20782,13 +20785,13 @@
     </row>
     <row r="38" spans="1:427">
       <c r="A38" s="1" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="D38" s="1"/>
       <c r="E38" s="1"/>
@@ -20995,10 +20998,10 @@
       <c r="GP38" s="1"/>
       <c r="GQ38" s="1"/>
       <c r="GR38" s="1" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="GS38" s="1" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="GT38" s="1"/>
       <c r="GU38" s="1"/>
@@ -21293,13 +21296,13 @@
     </row>
     <row r="39" spans="1:427">
       <c r="A39" s="1" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="D39" s="1"/>
       <c r="E39" s="1"/>
@@ -21506,10 +21509,10 @@
       <c r="GP39" s="1"/>
       <c r="GQ39" s="1"/>
       <c r="GR39" s="1" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="GS39" s="1" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="GT39" s="1"/>
       <c r="GU39" s="1"/>
@@ -21804,13 +21807,13 @@
     </row>
     <row r="40" spans="1:427">
       <c r="A40" s="1" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="D40" s="1"/>
       <c r="E40" s="1"/>
@@ -22011,10 +22014,10 @@
       <c r="GN40" s="1"/>
       <c r="GO40" s="1"/>
       <c r="GP40" s="1" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="GQ40" s="1" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="GR40" s="1"/>
       <c r="GS40" s="1"/>
@@ -22333,13 +22336,13 @@
     </row>
     <row r="41" spans="1:427">
       <c r="A41" s="1" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="D41" s="1"/>
       <c r="E41" s="1"/>
@@ -22540,10 +22543,10 @@
       <c r="GN41" s="1"/>
       <c r="GO41" s="1"/>
       <c r="GP41" s="1" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="GQ41" s="1" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="GR41" s="1"/>
       <c r="GS41" s="1"/>
@@ -22862,13 +22865,13 @@
     </row>
     <row r="42" spans="1:427">
       <c r="A42" s="1" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="D42" s="1"/>
       <c r="E42" s="1"/>
@@ -23005,7 +23008,7 @@
         <v>439</v>
       </c>
       <c r="DX42" s="1" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="DY42" s="1"/>
       <c r="DZ42" s="1" t="s">
@@ -23311,13 +23314,13 @@
     </row>
     <row r="43" spans="1:427">
       <c r="A43" s="1" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="D43" s="1"/>
       <c r="E43" s="1"/>
@@ -23454,7 +23457,7 @@
         <v>439</v>
       </c>
       <c r="DX43" s="1" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="DY43" s="1"/>
       <c r="DZ43" s="1" t="s">
@@ -23760,13 +23763,13 @@
     </row>
     <row r="44" spans="1:427">
       <c r="A44" s="1" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="D44" s="1"/>
       <c r="E44" s="1"/>
@@ -24197,13 +24200,13 @@
     </row>
     <row r="45" spans="1:427">
       <c r="A45" s="1" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="D45" s="1"/>
       <c r="E45" s="1"/>
@@ -24634,13 +24637,13 @@
     </row>
     <row r="46" spans="1:427">
       <c r="A46" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="D46" s="1"/>
       <c r="E46" s="1"/>
@@ -25075,13 +25078,13 @@
     </row>
     <row r="47" spans="1:427">
       <c r="A47" s="1" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="D47" s="1"/>
       <c r="E47" s="1"/>
@@ -25516,13 +25519,13 @@
     </row>
     <row r="48" spans="1:427">
       <c r="A48" s="1" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="D48" s="1"/>
       <c r="E48" s="1"/>
@@ -25953,13 +25956,13 @@
     </row>
     <row r="49" spans="1:427">
       <c r="A49" s="1" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="D49" s="1"/>
       <c r="E49" s="1"/>
@@ -26390,13 +26393,13 @@
     </row>
     <row r="50" spans="1:427">
       <c r="A50" s="1" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="D50" s="1"/>
       <c r="E50" s="1"/>
@@ -26827,13 +26830,13 @@
     </row>
     <row r="51" spans="1:427">
       <c r="A51" s="1" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="D51" s="1"/>
       <c r="E51" s="1"/>
@@ -27264,13 +27267,13 @@
     </row>
     <row r="52" spans="1:427">
       <c r="A52" s="1" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="D52" s="1"/>
       <c r="E52" s="1"/>
@@ -27709,13 +27712,13 @@
     </row>
     <row r="53" spans="1:427">
       <c r="A53" s="1" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="D53" s="1"/>
       <c r="E53" s="1"/>
@@ -28154,13 +28157,13 @@
     </row>
     <row r="54" spans="1:427">
       <c r="A54" s="1" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="D54" s="1"/>
       <c r="E54" s="1"/>
@@ -28591,13 +28594,13 @@
     </row>
     <row r="55" spans="1:427">
       <c r="A55" s="1" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="D55" s="1"/>
       <c r="E55" s="1"/>
@@ -29028,13 +29031,13 @@
     </row>
     <row r="56" spans="1:427">
       <c r="A56" s="1" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="D56" s="1"/>
       <c r="E56" s="1"/>
@@ -29473,13 +29476,13 @@
     </row>
     <row r="57" spans="1:427">
       <c r="A57" s="1" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="D57" s="1"/>
       <c r="E57" s="1"/>
